--- a/disease_registry/outputs/Soybean/internet.xlsx
+++ b/disease_registry/outputs/Soybean/internet.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,12 +471,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stem, Pod, Seed, Foliar</t>
+          <t>Stem, Pod, Foliar, Seed, Root</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Brown, irregularly shaped spots on stems, pods and petioles; seedlings develop sunken, dark brown lesions on cotyledons that may expand to stems; dark acervuli (pin cushion-like structures) develop in lesions on all tissue areas. Infected leaves develop brown veins and curl up, and brown cankers can appear on petioles causing defoliation.. Dark bodies looking like 'pin cushions' (acervuli) on plant surface visible at 20X magnification or greater; tiny black spines (setae) visible with 10X hand lens on infected areas; brown irregularly shaped spots on stems, pods and petioles; pod blanking where mycelium completely fills pod cavity.. Pod and stem blight</t>
+          <t>Red to brown dark irregular lesions appear on stems, pods, and petioles covered with black fruiting bodies (acervuli) containing spines (setae); affected leaves show vein reddening and rolling; symptoms are often not visible until plants approach maturity.. Black fruiting bodies (acervuli) containing spines (setae) visible as black dots on infected tissue surface; tiny black spines (setae) also visible with a 10X hand lens on infected areas. Pod and stem blight</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,47 +491,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bacterial_Blight</t>
+          <t>Alfalfa_Mosaic_Virus</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pseudomonas syringae pv. glycinea</t>
+          <t>Alfalfa mosaic virus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Foliar, Stem, Pod, Seed</t>
+          <t>Foliar, Seed, Whole plant</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Infections begin as small, angular, water-soaked spots that turn yellow and then brown as the tissue dies. Lesions have dark reddish-brown centers surrounded by yellowish-green halos around water-soaked tissue; lesions may coalesce to form large, irregularly shaped lesions. Leaf veins may become affected creating necrotic areas resembling lightning on the leaf. Eventually lesions fall out leaving ragged foliage.. Presence of a yellowish-green halo around lesions; most common on young leaves in mid to upper canopy whereas brown spot is usually seen on older, lower leaves; lack of fungal structures in lesions.. Septoria brown spot, brown spot</t>
+          <t>Symptoms vary from wilting, white flecks, malformation like dwarfing, ringspots, mottles, mosaics to necrosis depending on the virus strain, host variety, stage of growth at infection and environmental conditions.. Necrosis and yellow mosaics on affected plant tissues</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brown_Stem_Rot</t>
+          <t>Pod_And_Stem_Blight</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Phialophora gregata</t>
+          <t>Diaporthe sojae and Diaporthe longicolla</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -541,17 +541,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stem, Foliar, Root, Vascular</t>
+          <t>Foliar, Stem, Pod, Seed</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brown discoloration of the stem pith, especially at and between nodes near the soil line; foliar symptoms include interveinal chlorosis and necrosis (yellowing and browning of tissue between leaf veins), followed by leaf wilting and curling.. Brown discoloration of the pith (internal stem tissue), best observed at full pod stage; the pith remains brown unlike in sudden death syndrome where it stays white or cream-colored.. Sudden Death Syndrome</t>
+          <t>The most obvious sign of pod and stem blight is the presence of pycnidia on infected material - small, black spore-producing structures first seen on leaf petioles that form linear rows on stems, clusters near nodes, and scattered arrangements on pods, with infected seeds appearing shriveled, cracked, or chalky.. The appearance of lines of pycnidia covering large sections of the stem or occurring in clusters near the nodes are the most definitive diagnostic features.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -561,27 +561,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bean_Pod_Mottle_virus</t>
+          <t>Bacterial_Pustule</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bean pod mottle virus (BPMV)</t>
+          <t>Xanthomonas axonopodis pv. glycines</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Foliar, Pod, Stem, Seed</t>
+          <t>Foliar, Pod</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Symptoms range from mild chlorotic mottling of foliage to severe mosaic on younger leaves, with possible leaf distortion, stunting, puckering, and reduced pod size in severe infections. Seeds from infected plants may be mottled or discolored. Green stem syndrome may also occur.. Symptom development favored by cool temperatures but may not be apparent at higher temperatures or after pod set. No physical signs of the pathogen are present; confirmation requires lab testing. BPMV may also cause green stem syndrome where plants retain green stems and leaves after pods and nearby plants have matured.. Soybean mosaic virus</t>
+          <t>Symptoms begin as small, light green spots (not water-soaked) with raised centers on the upper and lower surfaces of leaves. Light-colored pustules (blisters) often develop in the center of lesions, especially on the undersides of leaves. The lesions can grow together into large irregular brown areas.. Bacterial pustule can be differentiated by a lack of water soaking at the initial site of infection, less chlorosis around lesions, and by the formation of tiny tan bumps on the undersides of leaves. Unlike soybean rust, bacterial pustule pustules lack an opening in the pustules or masses of spores. If an opening is present, it is typically a linear crack across the surface of the pustule.. Soybean rust, Bacterial blight</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -590,33 +590,33 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cercospora</t>
+          <t>Bean_Pod_Mottle_Virus</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cercospora kikuchii</t>
+          <t>Bean pod mottle virus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fungal</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Foliar, Stem, Pod, Seed</t>
+          <t>Foliar, Pod, Seed, Stem, Whole plant</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The first symptom is the development of light purple spots and areas on the top surface of leaves exposed to light. The discolored areas expand and deepen in color to a reddish-purple or bronze. The infected leaves appear leathery and 'sunburned'. Red-brown spots may develop on both leaf surfaces and may coalesce to form large necrotic areas, eventually resulting in defoliation of infected leaves in the upper canopy.. Purple-bronze discoloration on leaf surface caused by cercosporin toxin produced in the presence of light; small dark spots along major leaf veins and petioles; leaves wrinkle and become tough as disease progresses. Reddish-purple lesions on petioles, stems, and pods; pink to purple discoloration on seed coats.</t>
+          <t>Symptoms first appear on younger leaves and range from mild chlorotic mottling of foliage to severe mosaic with rugosity (distortion or wrinkling) on foliage and pods, accompanied by stunting and delayed maturity. Severe infections also produce leaf distortion, puckering, and reduced pod size. Seed coat mottling with black or brown pigmentation bleeding from the hilum is also observed.. Rugosity and chlorotic mottling on leaves and pods. Green stem where the stem remains green after the soybean pods have matured. Seed coat mottling with black or brown pigmentation bleeding from the hilum.. Herbicide injury, Other viruses</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -631,12 +631,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Purple_Seed_Stain</t>
+          <t>Brown_Spot</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cercospora kikuchii</t>
+          <t>Septoria glycines</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Seed, Pod</t>
+          <t>Foliar, Stem, Pod</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pink to purple discoloration on seed coats of infected seeds; soybean pods infected by C. kikuchii develop purple seed stain.. Pink to purple discoloration specifically on seed coats</t>
+          <t>Angular, red to brown spots appear on leaves that vary from tiny specks to quarter-inch diameter, causing affected leaves to turn yellow and fall to the ground; defoliation proceeds from the bottom of the plant toward the top. Initial symptoms are small dark brown spots (less than 1/8 inch) that appear first on lower leaves and progress upward.. Angular red to brown lesions of varying sizes on leaf surfaces; brown areas contain tiny raised specks called pycnidia (visible with a hand lens) where spores are produced; rapid yellowing of heavily spotted leaves; irregular brown lesions with indefinite borders may also appear on pods, stems, and petioles.. Bacterial blight, Soybean rust</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -660,18 +660,18 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bacterial_Pustule</t>
+          <t>Bacterial_Blight</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Xanthomonas axonopodis pv. glycines</t>
+          <t>Pseudomonas syringae pv. glycinea</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -681,12 +681,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Foliar, Pod</t>
+          <t>Foliar, Stem, Pod, Seed</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Small, light green spots with raised centers on leaf surfaces that develop into light-colored pustules (blisters), especially on undersides of leaves. Lesions can grow together into large irregular brown areas, and small raised spots may also develop on pods.. Lack of water soaking at initial infection site, less chlorosis around lesions, tiny tan bumps on undersides of leaves without openings or spore masses (unlike soybean rust pustules). If an opening is present on the pustule, it is typically a linear crack across the surface.. Bacterial blight, Soybean rust</t>
+          <t>Early season infection shows brown spots on cotyledons. Later symptoms include angular lesions on leaves progressing from yellow-brown to dark reddish-brown centers with yellowish-green halos around water-soaked tissue, spots merging into large dead patches; infected tissue may fall out giving leaves a ragged appearance.. Angular lesions with dark reddish-brown centers and a distinctive yellowish-green halo around water-soaked tissue; lack of fungal structures in lesions. Septoria brown spot, brown spot (Septoria glycines)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -701,27 +701,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Charcoal_Rot</t>
+          <t>Soybean_Mosaic_Virus</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina</t>
+          <t>Soybean mosaic virus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fungal</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Root, Stem, Foliar, Vascular, Pod, Seed</t>
+          <t>Foliar, Seed, Pod, Whole plant</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brown to dark spots on cotyledons at seedling stage; circular to oblong reddish-brown to black lesions at unifoliate stage; light brown to grey superficial stem lesions mid to late season; roots and stems near soil surface appear gray with tiny black specks or dots resembling charcoal dust; cross-sections of lower stem and taproot streaked with gray hyphae and microsclerotia giving a marbled appearance; reddish-brown discoloration in pith and vascular tissues; plants may be stunted and wilted with small chlorotic and necrotic leaves that remain attached.. Presence of microsclerotia in vascular tissue, pith, and mature dry pods; marbled appearance of cross-sections of lower stem and taproot with gray hyphae and microsclerotia; small black spots (pycnidia) irregularly dispersed across stem surface; tiny black specks or dots resembling charcoal dust on or just inside the tissue surface.</t>
+          <t>Symptoms range from no apparent symptoms to severely mottled and deformed leaves with light and dark green patches. Infected leaf blades become puckered along veins and curled downward. The disease causes plant stunting, reduced seed size, and reduced pod number. Seeds may also develop mottling symptoms.. Mottled leaves with contrasting light and dark green patches most obvious on young, rapidly growing leaves, with leaf blades puckered along veins and curled downward; combined with chlorosis between dark green areas.. growth regulator herbicide damage, Bean pod mottle virus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -730,18 +730,18 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Frogeye_leaf_spot</t>
+          <t>Phomopsis</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cercospora sojina</t>
+          <t>Phomopsis spp.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -751,52 +751,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Foliar, Stem, Pod, Seed</t>
+          <t>Seed</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Early symptoms are small, dark, water-soaked circular to angular lesions (generally 1-5 mm diameter) that expand into brown to grayish spots with brown-reddish borders. A yellow halo may be present around leaf spots. Centers of spots may show small black dots (spores) or fall away leaving a 'shot hole' appearance.. The reddish-brown or purple ring surrounding round leaf spots distinguishes frogeye leaf spot. Small black dots resembling fine ground pepper (fungal spores) visible in the middle of lesions.</t>
+          <t>Phomopsis fungi reduce seed quality.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Diaporthe</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Diaporthe sojae</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Fungal</t>
-        </is>
-      </c>
+          <t>Brown_Stem_Rot</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stem, Pod</t>
+          <t>Foliar, Stem</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Parallel rows of black, flask-shaped specks or pycnidia on mature soybean stems occurring later in the season (R6 to R8 growth stages). Pycnidia may also develop on dry, poorly developed pods, but may be dispersed randomly rather than arranged linearly.. Parallel rows of black, flask-shaped pycnidia arranged linearly on stems; random dispersal on pods.</t>
+          <t>Similar leaf symptoms to SDS, but with tan to brown pith at or near the crown and at leaf nodes. Tan to brown pith at crown and leaf nodes distinguishes it from SDS, which has white pith. Sudden Death Syndrome</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -806,12 +798,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Phomopsis</t>
+          <t>Sudden_Death_Syndrome</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Phomopsis longicola</t>
+          <t>Fusarium virguliforme</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -821,82 +813,70 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>Root, Stem, Vascular, Foliar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Infected seed are cracked, shriveled, dull, and may have a gray mold on them.. Seed infected by pod and stem blight may decompose after harvest and have low viability; seedlings grown from infected seeds may often be blighted.</t>
+          <t>Root symptoms include necrosis and dieback with brown vascular discoloration extending to the lower stem. Foliar symptoms develop with interveinal chlorotic spots that become necrotic, with leaflets eventually detaching from petioles while the central vein remains green.. White pith at the crown distinguishes SDS from Brown Stem Rot, which has tan to brown pith. Blue-green masses of macroconidia may be visible on roots close to the soil line, and interveinal chlorosis with central vein remaining green on leaves.. Brown Stem Rot, Fusarium wilt, Phytophthora root rot, white mold, soybean vein necrosis virus, taproot decline</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Phyllosticta_leaf_spot</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Phyllosticta sojicola</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Fungal</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Foliar</t>
-        </is>
-      </c>
+          <t>Soybean_Rust</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lesions most often occur on leaves and are circular, oval, and irregular or V-shaped. Lesions appear gray or tan and have a narrow, dark margin. Irregularly shaped tan/brownish lesions with purplish margins may be observed in the lower canopy.. In older lesions, numerous small, black specks (i.e., pycnidia) may be visible.</t>
+          <t>Soybean rust pustules have an opening and masses of spores, unlike bacterial pustule.. bacterial pustule</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Phytophthora</t>
+          <t>Cercospora_Blight</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Phytophthora sojae</t>
+          <t>Cercospora kikuchii</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oomycete</t>
+          <t>Fungal</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Root, Stem, Foliar</t>
+          <t>Foliar, Stem, Pod, Seed</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Young plants show rapid yellowing and wilting with soft rot and collapse of the root. Mature plants exhibit general yellowing of lower leaves progressing upward, followed by wilting and death, with brown discolored roots and a dark chocolate-brown stem discoloration extending from below the soil line upward several nodes; leaves typically stay attached after plant death.. The best diagnostic symptom on susceptible varieties is a lower stem discoloration (dark chocolate-brown) that may extend several nodes up the stem. Root system shows lateral and branch roots almost completely discolored; tap roots with brown surface discoloration and tan to brown inner tissue discoloration. Leaves turn yellow, wilt, and typically stay attached after plant death.. stem canker, Pythium</t>
+          <t>The first symptom of Cercospora leaf blight is the development of light purple spots and areas on the top surface of leaves exposed to light. The discolored areas expand and deepen in color to a reddish-purple or bronze. The infected leaves appear leathery and 'sunburned'. Infected seeds have pink to purple discoloration on the seed coats.. Light purple spots on upper leaf surfaces that expand and coalesce into large necrotic areas; leaves appear leathery and sunburned; reddish-purple lesions on petioles, stems, and pods; pink to purple discoloration on seed coats. Seed discoloration may range from small spots to coverage of the entire seed surface.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -905,18 +885,18 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Powdery_Mildew</t>
+          <t>Stem_Canker</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Erysiphe diffusa</t>
+          <t>Diaporthe phaseolorum var. caulivora and Diaporthe phaseolorum var. meridionalis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -926,32 +906,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Foliar, Pod, Seed</t>
+          <t>Stem, Leaves, Vascular tissue, Pod, Seed</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>White to gray powdery patches on leaves that begin small but coalesce to cover the entire leaf as disease progresses. Some varieties exhibit leaf yellowing, scorching, or rust-colored patch symptoms. Pods may become heavily infected resulting in shriveled, underdeveloped seed.. White, powdery coating on infected leaves that coalesces to cover the entire leaf; necrotic tissues may mimic herbicide injury symptoms.. herbicide injuries</t>
+          <t>Initial reddish-brown lesions appear at the base of branches or leaf petioles and on stems during early reproductive stages, progressing to dark brown or black sunken cankers that girdle and kill the stem. Foliage exhibits interveinal chlorosis that becomes necrotic; leaves may remain attached after death.. Sunken cankers enlarge longitudinally, turn dark brown to black, and girdle the stem; green stem tissue is usually present both above and below individual stem cankers; tiny black dots (perithecia or stroma/fruiting bodies) appear on dead stem tissue; reddish-brown discoloration may occur inside the stem; cankers typically form higher on the plant than Phytophthora.. Phytophthora rot</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Stem_Canker</t>
+          <t>Charcoal_Rot</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Diaporthe caulivora</t>
+          <t>Macrophomina phaseolina</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -961,12 +941,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Stem, Foliar, Pod</t>
+          <t>Foliar, Stem, Root, Vascular</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Early symptoms are reddish-brown lesions at the base of branches or leaf petioles that develop into elongated, sunken, dark brown cankers spreading up and down the stem. Tiny black dots called perithecia may appear on the stem singly or in clustered groups on plants killed by stem canker. Leaves may develop necrosis and chlorosis between the veins.. Elongated, sunken, dark brown cankers on stems with tiny black perithecia. Reddish-brown discoloration may also occur inside the stem. Lesions often develop at and remain darker at nodes. Stem cankers do not impact the root, unlike Phytophthora root rot.. Phytophthora root rot, Southern stem canker</t>
+          <t>Infected plants become wilted and stunted; fungal structures called microsclerotia fill root and stem tissues, clogging vascular tissue and causing wilting, yellowing, and stunting. Characteristic charcoal-sprinkled appearance develops on roots and stems.. Small, dark, round fungal structures called microsclerotia visible in split lower stems or when outer bark is removed; characteristic charcoal-sprinkled appearance from small black specks beneath the epidermis and inside lower stem and taproot; reddish-brown discoloration in pith and vascular tissues of root and stem; light gray streaking on taproot and lower stem.. soybean cyst nematode injury, early senescence, drought stress, Diaporthe diseases</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -981,23 +961,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Green_stem_disorder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>Fusarium_Wilts</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Fusarium oxysporum</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Abiotic</t>
+          <t>Fungal</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Foliar, Stem, Pod</t>
+          <t>Foliar, Root, Stem, Vascular</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>All or part of the soybean plant remains green while the rest of the plant or neighboring plants mature, most commonly seen in stems, leaves or pods; stems remain moist while pods and seeds have ripened.. Stems and occasionally leaves remain green and moist after pods and seeds have ripened and turned brown; excessive leaves on plant and green stems when neighboring plants are near harvest maturity.</t>
+          <t>Root rot appears as reddish-brown to dark brown discolored roots and poor nodulation. Foliar symptoms of Fusarium wilt include scorching of the upper leaves, while middle and lower canopy leaves can turn chlorotic and later wither and drop from the plant. Infected plants have brown vascular tissue in the roots and stems and show wilting of the stem tips.. Brown vascular tissue in roots and stems, wilting of stem tips, and the absence of external decay or stem lesions above the soil line. In plant stems, the fungus may produce a purple to pink vascular discoloration.. Verticillium wilt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1006,53 +990,45 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sudden_death_syndrome</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Fusarium virguliforme</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Fungal</t>
-        </is>
-      </c>
+          <t>Green_Stem</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Root, Foliar, Stem, Vascular</t>
+          <t>Foliar, Stem, Pod, Seed</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Leaf symptoms begin as scattered yellow diffuse spots between veins that expand to become brown lesions surrounded by chlorotic areas; leaves may be cupped or curled. Brown to grey discolored areas develop in the vascular tissue of the lower stem. Roots may show surface blue fungal growth in moist conditions.. The pith remains white, which distinguishes SDS from brown stem rot.. Brown stem rot</t>
+          <t>Plants maintain green stems and sometimes leaves well past the time when they are normally brown and mature, while pods and seeds have ripened.. Stems remain green after pods and seeds have ripened and are brown and ready for harvest, with plant stems remaining moist.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fusarium</t>
+          <t>Fusarium_Disease</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fusarium oxysporum; Fusarium solani</t>
+          <t>Fusarium solani and Fusarium oxysporum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1062,53 +1038,65 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Root, Foliar, Stem, Vascular</t>
+          <t>Root, Foliar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Root rot appears as reddish-brown to dark brown discolored roots with poor nodulation and cortical decay or vascular discoloration. Foliar symptoms include interveinal chlorosis, scorching of upper leaves, wilting, and defoliation. Infected plants have brown vascular tissue in roots and stems.. Brown vascular tissue in roots and stems with wilting of stem tips; no external decay or stem lesions above the soil line. Reddish to brown vascular discoloration extending into the lower stem. Secondary roots may develop above decomposed lateral roots on the upper taproot.. Pythium, Phytophthora, Rhizoctonia</t>
+          <t>Lower taproot and lateral roots appear brown to black with cortical decay or vascular discoloration. If severe, infected plants develop foliar symptoms including stunting, leaf yellowing, wilting, and defoliation.. Brown to black discoloration of lower taproot and lateral roots with cortical decay and vascular discoloration; lateral roots die and decompose with secondary roots developing above them on the upper taproot.. Pythium, Phytophthora, Rhizoctonia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Downy_mildew</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+          <t>Phytophthora</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Phytophthora sojae</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Oomycete</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Root, Stem, Foliar, Whole plant</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Young plants show rapid yellowing, wilting, soft rot, and root collapse; mature plants exhibit general yellowing of lower leaves progressing upward, wilting, and severe root discoloration with lower stem lesions.. Lower stem discoloration extending several nodes up the stem; severely discolored lateral and branch roots; tap roots with brown surface discoloration and tan to brown inner tissue discoloration when split.</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pythium_damping_off</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Globisporangium species (formerly Pythium species)</t>
-        </is>
-      </c>
+          <t>Pythium_Diseases</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>Oomycete</t>
@@ -1121,26 +1109,30 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Infected seeds appear rotted with soil sticking to them, and infected seedlings develop water-soaked lesions on the hypocotyl or cotyledons that turn into brown soft rot, with rotted roots that allow diseased plants to be easily pulled from soil. Symptomatic areas of plants can range in color from light tan to almost black.. Water-soaked lesions developing into brown soft rot on seedlings, with rotted roots that cause plants to pull easily from soil, and rotted seeds with soil sticking to them.. Phytophthora, Fusarium, Rhizoctonia</t>
+          <t>Damping-off causes rotting and death of seeds and seedlings, with pre-emergence seed failure and decay in soil, and post-emergence root lesions and discoloration leading to root rot and seedling collapse.. Pythium damping-off presents in two distinct stages: pre-emergence damping-off with seed failure and disintegration in soil, and post-emergence damping-off with root lesions, discoloration, and root rot. Young seedlings are highly susceptible while adult plants are resistant due to thicker and lignified root tissue.. Phytophthora sojae damping-off, Fusarium damping-off, Rhizoctonia damping-off</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rhizoctonia</t>
+          <t>Rhizoctonia_Damping-Off</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
@@ -1155,27 +1147,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Septoria_brown_spot</t>
+          <t>Iron_Deficiency_Chlorosis</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Septoria glycines</t>
+          <t>Unknown — abiotic/physiological disorder (iron deficiency)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fungal</t>
+          <t>Abiotic</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Foliar, Stem, Pod, Seed</t>
+          <t>Leaves</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Angular, red to brown spots varying from tiny specks to quarter-inch diameter appear on upper and lower leaf surfaces. Leaves with numerous spots rapidly turn yellow and fall to the ground. Defoliation proceeds from the bottom of the plant toward the top. Light to dark brown necrotic regions often with chlorosis surrounding the necrotic region progress from lower to middle canopy.. The brown areas can contain tiny raised specks called pycnidia (visible with a hand lens) where spores are produced. Spots are angular, red to brown in color, varying from tiny specks to quarter-inch diameter, with premature yellowing and defoliation starting from lower leaves progressing upward.. soybean rust, Bacterial blight</t>
+          <t>Iron deficiency inhibits chlorophyll synthesis, causing interveinal chlorosis — pale-yellow leaves with green veins — appearing first on the youngest (uppermost) leaves. In severe cases, leaves turn white and plant growth may be severely stunted.. Symptoms appear first on the youngest (top) leaves with yellow coloration between green veins (interveinal chlorosis), while older trifoliolate leaves remain entirely green. Iron is not mobile within the plant, so newly formed leaves are affected first. This pattern distinguishes IDC from atrazine injury, where yellowing occurs on the lowest leaves first.. Atrazine injury, Nitrogen deficiency, Potassium deficiency, Glyphosate injury, Group 2 ALS inhibitor herbicide injury, Manganese deficiency, Soybean cyst nematode (SCN)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1184,37 +1176,53 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Soybean_Cyst_Nematode</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+          <t>Downy_Mildew</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Peronospora manshurica</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Oomycete</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Foliar, Pod, Seed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Lesions appear as irregularly shaped, pale green to light yellow spots on upper leaf surfaces that enlarge and turn brown with yellow-green margins. Fuzzy, gray tufts grow on the leaf underside, while infected pods contain a dried, whitish fungal mass internally.. Fuzzy, gray tufts on leaf underside; dried, whitish crusty fungal mass inside pods and seeds; infected seed smaller, dull white, and cracked. If in doubt, place the leaf in a plastic bag with a moist paper towel and examine again for sporulation in about 6 hours.. Common soybean viruses, White mold</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>White_Mold</t>
+          <t>Frogeye_Leaf_Spot</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sclerotinia sclerotiorum</t>
+          <t>Cercospora sojina</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1224,52 +1232,44 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Stem, Foliar, Pod, Seed</t>
+          <t>Foliar</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>White mold is recognized by fluffy, white growth on soybean stems with gray to white lesions at nodes that rapidly progress and girdle stems. Lesions expand and plant tops become grayish-green, then wilt and die. Dead leaves remain attached to stems while turning brown, and characteristic black sclerotia are visible embedded within white mold on stem lesions. Dry dead stems develop a bleached white appearance.. Characteristic black sclerotia embedded within white fluffy mold on stems and inside stems as the plant approaches death; dead leaves remaining attached to stems while turning completely brown; white cottony seeds in pods.. Bird's nest fungi</t>
+          <t>Small brown lesions ⅛ to ¼ inch across with pale brown to white centers and dark brown margins, round to irregular in shape.. Small lesions with pale brown to white centers contrasting with dark brown margins; smaller size than target spot. Target spot</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Top_Dieback</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Phomopsis spp. / Diaporthe spp.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Fungal</t>
-        </is>
-      </c>
+          <t>Potassium_Deficiency</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Foliar, Seed</t>
+          <t>Foliar</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Initial symptoms appear as bright yellowing and tissue death on outer leaf margins of upper canopy leaves in early to mid August, followed by discoloration at nodes, brown edges, ragged appearance as dead tissue falls out, and eventual whole leaf death with small shriveled seeds at maturity. The uppermost leaves turn yellow/brown along the leaf margins.. Symptoms occur on upper/new plant leaves rather than lower leaves, and affected plants often follow row patterns or specific field areas. Unlike potassium deficiency, yellowing and browning is along leaf margins of the uppermost new leaves.. Potassium Deficiency, Sudden Death Syndrome</t>
+          <t>Yellowing, reddening, and dying of leaf margins on lower (older) leaves during vegetative growth and on upper (younger) leaves during grain fill, with stunted plants and slow growth. Yellowing begins at the leaf tip and extends down the margins toward the leaf base; in severe cases leaf edges become brown and necrotic.. Margin necrosis (yellowing, reddening, and dying) starting on leaf edges; symptoms appear on older leaves first during vegetative stage and on newer leaves during grain fill; yellowing begins at leaf tip and extends downward along margins; plant stunting and reduced growth.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1279,149 +1279,895 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tobacco_Streak_Virus</t>
+          <t>Powdery_Mildew</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tobacco streak virus</t>
+          <t>Erysiphe diffusa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Fungal</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Foliar, Stem, Seed, Pod, Whole plant</t>
+          <t>Foliar, Pod</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Symptoms include bud blight, shepherd's crooking, stunting, wilting, delayed maturity, bud and leaf proliferation, reduced pod number, discolored, distorted, and dead leaves, discoloration and dead streaks at nodes, dark spots on pods, and delayed seed development.. Pod lesions, proliferation of tissue, discoloration and dead streaks at nodes, dark spots on pods, and seed discoloration are characteristic features.</t>
+          <t>White to light gray, powdery fungal growth covers the upper surface of leaves; white to gray powdery patches begin small and coalesce to cover the entire leaf as the disease progresses. Later symptoms include leaf tissue yellowing and premature leaf drop.. White to gray powdery patches on leaves, most commonly in the mid to lower canopy. Some varieties exhibit additional symptoms including leaf yellowing, scorching, or rust-colored patches.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Diaporthe_2015_Kanawha</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+          <t>Purple_Seed_Stain</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cercospora flagellaris</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Seed, Foliar, Stem</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Infected seeds display pink to purple spots ranging from specks to large blotches covering the entire surface; leaves show dark reddish-purple bronzing with irregular lesions.. Discoloration extends from the seed hilum in all cases; dark reddish-purple bronzing on leaves; sunken red lesions on stems and petioles up to ¼ inch in length.</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Fusarium_healthy_vs_infected</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+          <t>Phymatotrichum_Root_Rot</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Phymatotrichopsis omnivora</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Root, Foliar, Whole plant</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Patches of wilted plants that rapidly die in row crops, with affected areas expanding to form circular regions of dead plants; leaves dry, turn brown, and remain attached; taproots become severely decayed. Leaves show slight yellowing and bronzing followed by wilting; a reddish lesion may develop around the crown. Brown fungal growth (mycelium) may be visible on root surfaces.. Spore mats forming on soil surface as circular patches of white moldy growth that turn tan in color before dissipating; decayed roots partly covered by fuzzy, tan-colored mold (mycelium); bark readily strips from decayed roots revealing reddish brown stain along white woody tissue. Fungal strands on infected roots show cruciform (cross-shaped) hyphae with pointed terminals unique to this fungus under microscopy.</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Green_stem</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>Phyllosticta_Leaf_Spot</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Phyllosticta sojicola</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Foliar</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Symptoms can appear as somewhat round, light to tan colored lesions with a dark border. Dark-colored 'specks' (pycnidia structures) form in the lesions rather than masses of spores.. Pycnidia structures visible as dark-colored 'specks' in lesions, distinguishing it from the spore masses of frogeye leaf spot. Frogeye leaf spot</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Soybean_Dwarf_Mosaic_Virus</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+          <t>Soybean_Cyst_Nematode</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Heterodera glycines</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Nematode</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Root, Vascular, Foliar, Whole plant</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Stunting and chlorosis of leaves are typical visual symptoms. "Yellow dwarf" is an appropriate description for symptoms commonly caused by SCN. Severely infected plants show stunting, impaired canopy development, and potentially chlorotic leaves. Often there are no obvious aboveground symptoms; significant yield loss can occur without any visible aboveground symptoms.. The unique diagnostic sign of SCN infection is the presence of living mature female nematodes or cysts attached to roots. These are tiny, lemon-shaped, white to yellow females, about 1/40 inch long and 1/60 inch wide, visible to the naked eye beginning 4-5 weeks after planting. They are easily distinguished from the much larger bacterial nodules on roots. Mature females are white; dead females turn brown forming cysts.. Iron-deficiency chlorosis, Potassium-deficiency symptoms, Nutrient deficiencies, Agricultural chemical injury, Soybean aphid feeding, Infection by other plant pathogens</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Soybean_Vein_necrosis_virus</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+          <t>Diaporthe</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Diaporthe longicolla</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Seed, Stem</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Infected seeds are cracked, shriveled, and covered with chalky white mold. Infected seedlings exhibit reddish-brown pinpoint lesions on cotyledons or reddish-brown streaks on stems near the soil line. Infected seed may also appear cracked, shriveled, dull, and covered with gray mold.. Seeds that are cracked, shriveled and covered with chalky, white mold.</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Soybean_rust</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+          <t>Soybean_Dwarf_Virus</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Soybean dwarf virus</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Foliar, Stem, Whole plant</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Leaves can be dark green, brittle, wrinkled, curled, small, and thick; plant stunting, green stem, delayed maturity, and yellowing between leaf veins occur.</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sclerotinia_Timber_Rot</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sclerotinia sclerotiorum</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Foliar, Stem, Pod</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Leaves wilt and turn gray-green before browning; diseased stem areas become tan and bleached with a pithy texture that shreds easily.. White fluffy mycelium and sclerotia on stem and pod surfaces distinguish this disease from other stem and root rot diseases.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Septoria_Brown_Spot</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Septoria glycines</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Foliar, Stem</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Symptoms begin as small brown spots with yellow halos that coalesce to turn leaves yellow, and infected leaves may drop prematurely.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Rhizoctonia</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rhizoctonia solani</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Seed, Root, Stem, Foliar</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Wilted or dead seedlings with reddish-brown, sunken lesions on hypocotyls and lower stems; older plants show chlorosis and stunted growth resembling nitrogen deficiency.. Distinct reddish-brown, sunken, dry cankers on the lower stem or hypocotyl; lesions can girdle the stem and kill or stunt plants, or remain superficial with minimal effects.. Pythium, Phytophthora</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>White_Mold</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sclerotinia sclerotiorum</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Foliar, Stem, Seed, Pod</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Lesions usually develop first at stem nodes during or after flowering. The tops of the plants become grayish-green and then wilt and die. Infected stems often become soft and watery, covered with white moldy growth in moist conditions, or develop a bleached white appearance when dry.. Hard, black sclerotia that resemble rodent droppings develop on or inside infected stems and pods; white fluffy mycelium covers stem lesions under moist conditions.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Taproot_Decline_On_Soybean</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Xylaria necrophora</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Foliar, Root, Seed, Whole plant</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Foliar symptoms include interveinal chlorosis and necrosis of leaves; affected roots exhibit black fungal growth and snap off when removed from soil, leaving most of the root system behind.. Black fungal growth on roots remaining attached to the stem; characteristic fungal fruiting bodies called 'dead man's fingers' appearing at the base of plants or in soil residue.. red crown rot, stem canker, sudden death syndrome</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Target_Spot</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Corynespora cassiicola</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Foliar, Stem, Pod, Seed, Root</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Round to irregular dark brown lesions roughly ½ inch across with concentric rings of varying brown shades and a yellow halo surrounding them; centers may fall out creating a shot-hole appearance as they age.. Relatively large lesions (½ inch) with prominent concentric rings in varying shades of brown and a distinctive yellow halo; mature lesions develop shot-hole symptoms. Frogeye leaf spot, Brown spot</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Soybean_Vein_Necrosis_Virus</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Foliar</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Sudden Death Syndrome</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>low</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Red_Crown_Rot_Of_Soybean</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Taproot Decline</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Herbicide_Injury</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Southern_Blight</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Tobacco_Ringspot_Virus</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Tobacco ringspot virus</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Foliar, Stem, Root, Pod, Vascular</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Tobacco ringspot virus causes shepherd's crooking, bud blight, stunting, wilting, delayed maturity, leaf discoloration and distortion, pith discoloration, petiole distortion, and poor root nodulation.. Shepherd's crooking is a prominent symptom, bud blight is characteristic of the disease, pith discoloration is evident, and delayed maturity is observable.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Tobacco_Streak_Virus</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Tobacco streak virus</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Foliar, Stem, Pod, Seed</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Symptoms of Tobacco streak virus (TSV) include bud blight, shepherd's crooking, stunting, wilting, delayed maturity, bud and leaf proliferation, reduced pod number, and discolored, distorted, and dead leaves. TSV infection can cause discoloration and dead streaks at nodes, dark spots on pods, and delayed seed development.. Pod lesions characteristic of tobacco streak; discoloration and dead streaks at nodes; seed discoloration; bud proliferation</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Top_Dieback</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Foliar, Stem, Seed</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Bright yellowing and tissue death appear on outer leaf margins in the upper plant canopy in early to mid-August, followed by node discoloration and browning of leaf edges with eventual whole leaf death. Severely affected plants may die prematurely.. Symptoms occur on upper leaves rather than lower leaves, distinguishing it from potassium deficiency; affected plants often follow row patterns or concentrate in specific field areas.. Potassium deficiency, Sudden Death Syndrome (SDS)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Wildfire_Of_Tobacco</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pseudomonas syringae pv. tabaci</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Bacterial_Pustule_Of_Soybean_Disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Cercospora</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Cercospora_Fungi</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Damping_Off</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Diaporthe_Fungus</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Pythium</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Rhizobium_Bacteria</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Root_And_Stem_Rot</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Septoria_Leaf_Blotch</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Soybean_Dwarf_Mosaic_Virus_2012</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Xylaria_Necrophora_Garcia-Aroca</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
         <v>0</v>
       </c>
     </row>
